--- a/output/2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx
@@ -536,10 +536,9 @@
           <t>+60 14-937 2872</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Produttore/fornitore B2B con pagine dedicate "Dust Collector Supplier In Johor" e "Dust Collector Air Purifying System" sul sito ufficiale. Email generica non reperita.</t>
+          <t>Produttore/fornitore B2B con pagine dedicate "Dust Collector Supplier In Johor" e "Dust Collector Air Purifying System" sul sito ufficiale. Email generica non reperita. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -616,7 +615,6 @@
           <t>+607-234 2307 / WhatsApp +6019-727 3978</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>System integrator M&amp;E con servizio "Dust Collector System" esplicitamente elencato tra le offerte (oltre ad ACMV, cleanroom). Email non reperita.</t>
@@ -696,7 +694,6 @@
           <t>+6012-792 2192</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Produttore/distributore B2B con pagina prodotto dedicata "Dust Collector Supplier Malaysia" e filiale esplicita a Johor Bahru. Email sul sito risultata illeggibile/offuscata in più tentativi di verifica, non riportata per evitare invenzioni.</t>
@@ -714,7 +711,6 @@
           <t>DMAG TECHNICAL SDN BHD</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Skudai, Johor</t>
@@ -730,7 +726,6 @@
           <t>019-736 1558</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Nessun sito ufficiale reperito. Esistenza confermata su piu' directory indipendenti (infopages.net.my, Experian, mysbusiness.com, Facebook) come fornitore Air Pollution Control / Bag Filter Dust Collector, reg. 941474-V.</t>
@@ -859,7 +854,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Elencato sul sito ufficiale del produttore Purrite Filtration come Sales Agent/Distributor per la Malesia con sede a Johor Bahru; distribuisce filtri industriali/air filtration equipment/HEPA.</t>
+          <t>Elencato sul sito ufficiale del produttore Purrite Filtration come Sales Agent/Distributor per la Malesia con sede a Johor Bahru; distribuisce filtri industriali/air filtration equipment/HEPA. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/output/2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
